--- a/Dataset.xlsx
+++ b/Dataset.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\da2\Desktop\Masoud Projects\DA\2026\3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SG\it353-or-any-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE1CA020-FDEF-4663-B1B2-8F14B9E71ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="12580"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -285,7 +284,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0\%"/>
@@ -348,19 +347,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{79AC67CF-DE81-42C2-BC22-278F35DBCEA2}" name="Data" displayName="Data" ref="A1:J36" totalsRowShown="0">
-  <autoFilter ref="A1:J36" xr:uid="{79AC67CF-DE81-42C2-BC22-278F35DBCEA2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Data" displayName="Data" ref="A1:J36" totalsRowShown="0">
+  <autoFilter ref="A1:J36"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{86C13F1E-CA83-49F8-AB4C-70D6079010E4}" name="Student ID"/>
-    <tableColumn id="2" xr3:uid="{983461B9-361F-454F-B73C-B9554FE68303}" name="Name"/>
-    <tableColumn id="3" xr3:uid="{647D1A1F-5588-451E-B916-6454F031D56A}" name="Test 1"/>
-    <tableColumn id="4" xr3:uid="{C4F0ED1F-78D9-4155-A628-DAB0827C9E41}" name="Test 2"/>
-    <tableColumn id="5" xr3:uid="{30784E52-035F-42B6-ABD4-9E2DA95C732C}" name="Test 3"/>
-    <tableColumn id="6" xr3:uid="{7196C711-5DAC-49C1-846B-3DE2D7B0D553}" name="Average" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{2297E3D6-447E-4773-8DA8-9F1100A8B115}" name="Attendance %" dataDxfId="0"/>
-    <tableColumn id="8" xr3:uid="{007C457E-E950-4B54-8A43-50585BF61408}" name="Academic Status"/>
-    <tableColumn id="9" xr3:uid="{0AC40DBE-7B9E-475B-8A0D-9B509CE3895A}" name="Attendance Status"/>
-    <tableColumn id="10" xr3:uid="{DA6C20DB-B96C-45BD-86C0-D138EE7D794F}" name="Risk Category"/>
+    <tableColumn id="1" name="Student ID"/>
+    <tableColumn id="2" name="Name"/>
+    <tableColumn id="3" name="Test 1"/>
+    <tableColumn id="4" name="Test 2"/>
+    <tableColumn id="5" name="Test 3"/>
+    <tableColumn id="6" name="Average" dataDxfId="1"/>
+    <tableColumn id="7" name="Attendance %" dataDxfId="0"/>
+    <tableColumn id="8" name="Academic Status"/>
+    <tableColumn id="9" name="Attendance Status"/>
+    <tableColumn id="10" name="Risk Category"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -628,19 +627,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J36"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.77734375" customWidth="1"/>
-    <col min="6" max="6" width="9.77734375" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" customWidth="1"/>
-    <col min="8" max="8" width="16.77734375" customWidth="1"/>
-    <col min="9" max="9" width="18.33203125" customWidth="1"/>
-    <col min="10" max="10" width="14.21875" customWidth="1"/>
+    <col min="1" max="1" width="11.81640625" customWidth="1"/>
+    <col min="6" max="6" width="9.81640625" customWidth="1"/>
+    <col min="7" max="7" width="14.54296875" customWidth="1"/>
+    <col min="8" max="8" width="16.81640625" customWidth="1"/>
+    <col min="9" max="9" width="18.36328125" customWidth="1"/>
+    <col min="10" max="10" width="14.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -672,7 +671,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -704,7 +703,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -736,7 +735,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -768,7 +767,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -800,7 +799,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -832,7 +831,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -864,7 +863,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -896,7 +895,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -928,7 +927,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -960,7 +959,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -992,7 +991,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -1024,7 +1023,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -1056,7 +1055,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -1088,7 +1087,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>41</v>
       </c>
@@ -1120,7 +1119,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -1152,7 +1151,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>45</v>
       </c>
@@ -1184,7 +1183,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -1216,7 +1215,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1248,7 +1247,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -1280,7 +1279,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>53</v>
       </c>
@@ -1312,7 +1311,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -1344,7 +1343,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>57</v>
       </c>
@@ -1376,7 +1375,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>59</v>
       </c>
@@ -1408,7 +1407,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -1440,7 +1439,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -1472,7 +1471,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -1504,7 +1503,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>67</v>
       </c>
@@ -1536,7 +1535,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>69</v>
       </c>
@@ -1568,7 +1567,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>71</v>
       </c>
@@ -1600,7 +1599,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>73</v>
       </c>
@@ -1632,7 +1631,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>75</v>
       </c>
@@ -1664,7 +1663,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>77</v>
       </c>
@@ -1696,7 +1695,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>79</v>
       </c>
@@ -1728,7 +1727,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>81</v>
       </c>
@@ -1760,7 +1759,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>83</v>
       </c>

--- a/Dataset.xlsx
+++ b/Dataset.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SG\it353-or-any-project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SG\Downloads\it353-or-any-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
